--- a/02_加值成品/九上/九上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-2 地震與火山　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上6-2 地震與火山　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>地震是岩層受力如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>斷裂錯動</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>趴下掩護穩住</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>板塊活動</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>釋放能量</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>地震以什麼傳播？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>地震波</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>趴下掩護穩住</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>傳遞</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>地震發生的地下位置是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>震源</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>發生處</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>震源正上方的地表是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>規模</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>溫泉肥沃土壤</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>震央</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>地表</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>表示地震能量大小的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>規模</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>震源</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>火山</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>表示某地搖晃程度的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>震度</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>規模</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>震源</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>搖晃</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>一個地震有幾個規模？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>一個</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>唯一</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>岩漿噴出地表是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>活動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>地震能量大小用什麼表示？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>規模</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>某處搖晃程度用什麼表示？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>規模</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>震度</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>搖晃</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-2 地震與火山　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上6-2 地震與火山　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>規模與震度差別？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>地震增多地表變形氣體逸出</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>皆與板塊活動釋放地球內能有關</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>規模每增能量呈倍數增加</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>能量vs搖晃程度</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>同一地震各地震度？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>可能不同</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>距離差</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>距震央越遠震度通常？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>板塊活動</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>越小</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>衰減</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>震源越淺災害常？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>板塊活動</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>震源</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>近地表</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>火山常與什麼活動伴隨？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>趴下掩護穩住</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>震央</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>板塊活動</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>震央在地表還地下？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>地表</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>正上方</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>地震規模數字越大能量？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>地震波</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>規模</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>火山</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>釋放多</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>火山帶來的好處舉例？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>趴下掩護穩住</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>溫泉肥沃土壤</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>益處</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>震源正上方的地表稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>震央</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>溫泉肥沃土壤</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>震度</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>地表</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>同一次地震規模有幾個？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>溫泉肥沃土壤</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>地表</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>一個</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>唯一</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上6-2 地震與火山　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上6-2 地震與火山　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何同一地震不同地方震度不同？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>規模每增能量呈倍數增加</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>能量vs搖晃程度</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>皆與板塊活動釋放地球內能有關</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>距震央遠近與地質不同影響搖晃</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>分布</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>規模增加對能量的影響很大原因？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>淺源能量近地表災害較大</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>偵測快波預警慢波到達前</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>規模每增能量呈倍數增加</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>能量vs搖晃程度</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>地震來時應如何保護自己？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>距震央遠近與地質不同影響搖晃</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>地震增多地表變形氣體逸出</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>趴下掩護穩住遠離掉落物</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>偵測快波預警慢波到達前</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>防災</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>震源深淺如何影響地表災害？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>位板塊交界活躍帶</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>皆與板塊活動釋放地球內能有關</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>地震增多地表變形氣體逸出</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>淺源能量近地表災害較大</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>深度</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>火山噴發前兆可能有？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>地震增多地表變形氣體逸出</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>淺源能量近地表災害較大</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>能量vs搖晃程度</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>規模每增能量呈倍數增加</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>監測</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>臺灣為何地震火山活動頻繁？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>位板塊交界活躍帶</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>淺源能量近地表災害較大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>規模每增能量呈倍數增加</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>能量vs搖晃程度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>位置</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何利用地震波差異做速報？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>淺源能量近地表災害較大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>趴下掩護穩住遠離掉落物</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>距震央遠近與地質不同影響搖晃</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>偵測快波預警慢波到達前</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>比較地震與火山的能量來源？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>皆與板塊活動釋放地球內能有關</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>淺源能量近地表災害較大</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>能量vs搖晃程度</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>規模每增能量呈倍數增加</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>離震央越遠震度通常如何？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>越小</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>震源</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>一個</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>可能不同</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>衰減</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>地震發生時正確的自保動作？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>地表</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>斷裂錯動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>趴下掩護穩住</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>震源</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>防災</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上6-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>釋放能量</t>
+          <t>釋放能量：地底岩層長期累積應力，當超過承受極限時會突然斷裂錯動，瞬間釋放出大量能量，這就是地震</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>傳遞</t>
+          <t>傳遞：地震發生時釋放的能量以地震波的形式向四面八方傳遞出去</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>發生處</t>
+          <t>發生處：地底下岩層真正斷裂、地震能量開始釋放的地方稱為震源</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>地表</t>
+          <t>地表：震源正上方對應到地表的位置稱為震央，通常是搖晃感受最明顯的地方之一</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：地震規模是用來表示一次地震釋放能量大小的數值</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>搖晃</t>
+          <t>搖晃：震度是描述某個地點實際感受到地震搖晃的劇烈程度</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>唯一</t>
+          <t>唯一：地震規模反映的是這次地震釋放的總能量，不論在哪裡測量都一樣，所以同一次地震只有一個規模值</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>活動</t>
+          <t>活動：地底岩漿透過地殼裂口噴發到地表的現象稱為火山活動</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：地震規模是用來表示地震釋放能量大小的數值,一次地震只有一個規模</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>搖晃</t>
+          <t>搖晃：震度是描述某個地點實際感受到的搖晃程度,同一次地震在不同地點的震度可能不同</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：地震規模是描述這次地震釋放的能量多寡，全世界都一樣只有一個數值；震度則是描述各地實際感受到的搖晃程度，會隨與震央的距離、地質條件而在不同地點各不相同</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>距離差</t>
+          <t>距離差：同一次地震在不同地點，因為距離震央遠近不同、當地地質條件不同，感受到的搖晃程度(震度)可能不一樣</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>衰減</t>
+          <t>衰減：地震波的能量會隨傳遞距離增加而逐漸減弱，所以離震央越遠的地方，感受到的震度通常越小</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>近地表</t>
+          <t>近地表：震源深度越淺，代表能量釋放的位置離地表越近，傳到地面時能量損失較少，通常造成的災害會比較嚴重</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：火山活動經常發生在板塊交界處，因為板塊運動使地底岩漿有機會沿裂縫湧出地表，兩者關係密切</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>正上方</t>
+          <t>正上方：震央是震源正上方對應到地表的位置，所以震央在地表上，震源才是在地下</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>釋放多</t>
+          <t>釋放多：地震規模數字越大，代表這次地震釋放的能量越多，而且規模每增加一定數值，能量會呈倍數大幅增加</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>益處</t>
+          <t>益處：火山活動雖然可能帶來災害，但也帶來一些益處，例如地熱形成溫泉可供利用，火山噴發物風化後也能形成肥沃的土壤</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>地表</t>
+          <t>地表：地下發生地震的地方叫震源,震源正上方對應到地表的位置就稱為震央</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>唯一</t>
+          <t>唯一：地震規模反映的是這次地震釋放的總能量,不論在哪裡測量都一樣,所以同一次地震只有一個規模值</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>分布</t>
+          <t>分布：地震波傳到不同地點時，因為距離震央的遠近不同、能量衰減程度不同，加上當地地質(如土壤鬆軟或岩盤堅實)也會放大或減弱搖晃，所以同一地震在不同地方感受到的震度會不同</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：地震規模的計算方式是對數尺度，規模每增加一個單位，釋放的能量並非只增加一點點，而是呈數十倍的倍數增加，所以規模看似相差不大，能量差異卻非常驚人</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>防災</t>
+          <t>防災：地震發生時建議立刻趴下、找掩護物保護頭頸部、並抓穩固定物，同時盡量遠離可能掉落的物品，減少受傷風險</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>深度</t>
+          <t>深度：震源越淺，代表能量從地底傳到地表的距離越短，衰減損失較少，抵達地面時威力仍然強大，因此淺源地震通常造成的地表災害比深源地震嚴重</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>監測</t>
+          <t>監測：火山噴發前，地底岩漿活動常會引發一連串小地震增多、地表因岩漿上湧而變形隆起、以及火山氣體從地表裂縫逸出增加等現象，這些都是可以監測的噴發前兆</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>位置：臺灣剛好位於歐亞板塊與菲律賓海板塊的交界處，板塊擠壓碰撞活動頻繁，所以地震和火山活動都比較活躍</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：地震波中傳播速度較快的P波先抵達，破壞力較大、速度較慢的S波隨後才到，地震速報系統利用先偵測到的P波，搶在破壞力強的S波抵達前發出警報，爭取避難時間</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>關聯：地震是板塊運動使岩層累積應力後突然斷裂釋放能量，火山則是板塊運動使地底岩漿獲得通道噴出地表，兩者的能量根本上都來自地球內部因板塊活動而釋放的內能，關係密切</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>衰減</t>
+          <t>衰減：地震波的能量會隨傳遞距離增加而逐漸減弱,所以離震央越遠的地方,感受到的震度通常越小</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>防災</t>
+          <t>防災：地震發生時建議立刻趴下、找掩護物保護頭頸、並抓穩固定物,減少被掉落物砸傷或跌倒受傷的風險</t>
         </is>
       </c>
     </row>
